--- a/data/original/business02.xlsx
+++ b/data/original/business02.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="202507071653000000" r:id="rId3" sheetId="1"/>
+    <sheet name="202508290938000590" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -90,13 +90,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="6.0" customWidth="true"/>
     <col min="2" max="2" width="36.0" customWidth="true"/>
     <col min="3" max="3" width="67.0" customWidth="true"/>
-    <col min="4" max="4" width="12.0" customWidth="true"/>
+    <col min="4" max="4" width="20.0" customWidth="true"/>
     <col min="5" max="5" width="12.0" customWidth="true"/>
     <col min="6" max="6" width="12.0" customWidth="true"/>
     <col min="7" max="7" width="12.0" customWidth="true"/>
@@ -104,7 +104,7 @@
     <col min="9" max="9" width="17.0" customWidth="true"/>
     <col min="10" max="10" width="6.0" customWidth="true"/>
     <col min="11" max="11" width="12.0" customWidth="true"/>
-    <col min="12" max="12" width="94.0" customWidth="true"/>
+    <col min="12" max="12" width="121.0" customWidth="true"/>
     <col min="13" max="13" width="36.0" customWidth="true"/>
     <col min="14" max="14" width="36.0" customWidth="true"/>
     <col min="15" max="15" width="9.0" customWidth="true"/>
@@ -113,10 +113,10 @@
     <col min="18" max="18" width="19.0" customWidth="true"/>
     <col min="19" max="19" width="9.0" customWidth="true"/>
     <col min="20" max="20" width="15.0" customWidth="true"/>
-    <col min="21" max="21" width="12.0" customWidth="true"/>
+    <col min="21" max="21" width="15.0" customWidth="true"/>
     <col min="22" max="22" width="12.0" customWidth="true"/>
     <col min="23" max="23" width="19.0" customWidth="true"/>
-    <col min="24" max="24" width="28.0" customWidth="true"/>
+    <col min="24" max="24" width="81.0" customWidth="true"/>
     <col min="25" max="25" width="24.0" customWidth="true"/>
     <col min="26" max="26" width="16.0" customWidth="true"/>
     <col min="27" max="27" width="19.0" customWidth="true"/>
@@ -415,12 +415,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>rbRCutPvSJ2DzYBMaNJhzA06491751878380</t>
+          <t>eAWLY3hPQlyRrgGWoFMHuQ06491756431539</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>随州配合</t>
+          <t>时代新安标定项目-卧龙水冷电机标定</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -440,32 +440,34 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>随州</t>
+          <t>苏州</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-07-05 下午</t>
+          <t>2025-09-01 上午</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-07-07 下午</t>
+          <t>2025-09-06 下午</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t/>
+          <t>1、拟定试验工作计划及进展
+2、电机标定
+3、电机故障灯问题及时处理解决</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -480,7 +482,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>尹娜</t>
+          <t/>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -490,17 +492,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>202507071653000008479</t>
+          <t>202508290938000596846</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-07-07 16:53:00</t>
+          <t>2025-08-29 09:38:59</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>贾海泉</t>
+          <t>程志鹏</t>
         </is>
       </c>
       <c r="T3"/>
@@ -516,35 +518,36 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2025-07-07 23:55:29</t>
+          <t>2025-08-29 11:41:15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>行政部</t>
+          <t>试验科</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>贾海泉提交的出差</t>
+          <t>程志鹏提交的出差</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>尹娜</t>
+          <t>张成林,李锋</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>7:2:29</t>
+          <t>2:2:17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>贾海泉|提交申请|2025-07-07 16:53:00|提交申请;
-尹娜|审批人|2025-07-07 23:55:29|同意;
-尹娜|直接主管|2025-07-07 23:55:29|同意;
-曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-07-07 23:55:29|抄送</t>
+          <t>程志鹏|提交申请|2025-08-29 09:38:59|提交申请;
+李锋|审批人|2025-08-29 10:34:44|同意|同意|;
+张成林|直接主管|2025-08-29 11:41:15|同意;
+李锋|直接主管|2025-08-29 11:41:15|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-29 11:41:15|抄送</t>
         </is>
       </c>
     </row>
@@ -556,420 +559,1265 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gs3luUiMQw2nXUHFpm5Z9w06491751420090</t>
+          <t>nV2tF7q0S9qHD0DLC-9ouQ06491756125817</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>沂源服务站动力总成更换</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>其他(私车公用)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>往返</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>青岛市</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>淄博市</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-08-26 上午</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-08-26 下午</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>沂源县润田服务站动力总成更换指导</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>杭州时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>宁德时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>202508252043000373918</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2025-08-25 20:43:37</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>薛宁</t>
+        </is>
+      </c>
+      <c r="T4"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2025-08-26 08:40:32</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>售后服务部</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>薛宁提交的出差</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>张成林</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>11:56:55</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>薛宁|提交申请|2025-08-25 20:43:37|提交申请;
+张成林|审批人|2025-08-26 08:40:32|同意;
+张成林|直接主管|2025-08-26 08:40:32|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-26 08:40:32|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KJYxlASeTReoZIrs3M4ACg06491755392384</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>考察双挂运煤</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>飞机</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>往返</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>格尔木</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-08-19 上午</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-08-21 上午</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>杭州时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>宁德时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>202508170859000440326</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2025-08-17 08:59:44</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>石启军</t>
+        </is>
+      </c>
+      <c r="T5"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>审批未通过</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2025-08-17 09:48:39</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>公司高管,杭州时代电动科技有限公司,制造中心,供应链管理部</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>石启军提交的出差</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>罗训强</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0:48:55</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>石启军|提交申请|2025-08-17 08:59:44|提交申请;
+罗训强|审批人|2025-08-17 09:48:39|拒绝|时代电动的在飞书上申请|</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M2t2aIzjT9G_cd27moIWXg06491754871588</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>时代新安项目标定</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>往返</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>苏州</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-08-11 上午</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-08-15 下午</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>杭州时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>宁德时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>202508110819000486303</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2025-08-11 08:19:48</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>程志鹏</t>
+        </is>
+      </c>
+      <c r="T6"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2025-08-11 09:54:02</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>试验科</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>程志鹏提交的出差</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>李锋,张成林</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1:34:14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>程志鹏|提交申请|2025-08-11 08:19:48|提交申请;
+李锋|审批人|2025-08-11 09:53:10|同意|同意|;
+张成林|直接主管|2025-08-11 09:54:02|同意|;
+李锋|直接主管|2025-08-11 09:54:02|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-11 09:54:02|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bww7ee5jTOeoamm5KBX80A06491754550387</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>返程</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>单程</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>襄阳</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-08-08 上午</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-08-08 下午</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>8月7号因电机三相线绝缘不过导致原定返程变动，产生退票手续费89元，特此申请望领导批示</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>杭州时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>宁德时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>202508071506000274408</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2025-08-07 15:06:27</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>秦国超</t>
+        </is>
+      </c>
+      <c r="T7"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2025-08-07 15:25:02</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>生产管理部</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>秦国超提交的出差</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>钟洪伟,董磊</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0:18:35</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>秦国超|提交申请|2025-08-07 15:06:27|提交申请;
+钟洪伟|审批人|2025-08-07 15:13:09|同意|;
+董磊|直接主管|2025-08-07 15:25:02|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-07 15:25:03|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Waw31FI9RUCnZstLr1f6uA06491754406755</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ea4000下线台架搭建</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>往返</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>随州</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-08-06 上午</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-08-09 下午</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>杭州时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>宁德时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>202508052312000353904</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2025-08-05 23:12:35</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>韦东略</t>
+        </is>
+      </c>
+      <c r="T8"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2025-08-05 23:12:41</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>试验科</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>韦东略提交的出差</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>程志鹏</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0:0:7</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>韦东略|提交申请|2025-08-05 23:12:35|提交申请;
+程志鹏|审批人|2025-08-05 23:12:41|同意;
+程志鹏|直接主管|2025-08-05 23:12:41|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-05 23:12:41|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>eVZ2WiCWQzWmGBI44mL2Lw06491754390681</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>协助随州生产线运行工艺，保障8月份生产订单交付</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>单程</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>随州市</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>随州市</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-08-01 上午</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-08-31 下午</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>杭州时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>宁德时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>202508051844000414650</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2025-08-05 18:44:41</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>祝叶康</t>
+        </is>
+      </c>
+      <c r="T9"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2025-08-05 18:53:45</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>工艺技术部</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>祝叶康提交的出差</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>董磊</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0:9:5</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>祝叶康|提交申请|2025-08-05 18:44:41|提交申请;
+董磊|审批人|2025-08-05 18:53:45|同意;
+董磊|直接主管|2025-08-05 18:53:46|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-05 18:53:46|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sBQFw5STQAm0NdizFmtlLA06491754299336</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>协助售后出差</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>往返</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>襄阳</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-08-04 下午</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-08-08 下午</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>杭州时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>宁德时代电动科技有限公司</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>202508041722000161130</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2025-08-04 17:22:16</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>秦国超</t>
+        </is>
+      </c>
+      <c r="T10"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>审批通过</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>已结束</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2025-08-04 17:25:58</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>生产管理部</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>秦国超提交的出差</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>钟洪伟,董磊</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0:3:42</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>秦国超|提交申请|2025-08-04 17:22:16|提交申请;
+钟洪伟|审批人|2025-08-04 17:22:27|同意;
+董磊|直接主管|2025-08-04 17:25:58|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-04 17:25:58|抄送</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>zsDqxpwZTRCNEGBLFwPhAw06491754095289</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>随州出差</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>火车</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>单程</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>杭州</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>随州</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2025-07-01 上午</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2025-07-31 下午</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-08-01 上午</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-08-31 下午</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">1、重卡生产线生产、调试，协助人员招聘、培训；
 2、重卡装配，发货
 </t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>杭州时代电动科技有限公司</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>宁德时代电动科技有限公司</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>202507020934000502481</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2025-07-02 09:34:50</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>202508020841000295765</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2025-08-02 08:41:29</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>段少波</t>
         </is>
       </c>
-      <c r="T4"/>
-      <c r="U4" t="inlineStr">
+      <c r="T11"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>审批通过</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>已结束</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2025-07-02 13:33:46</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2025-08-04 11:20:17</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>生产管理部,随州劳务</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>段少波提交的出差</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>董磊,钟洪伟</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>3:58:57</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>段少波|提交申请|2025-07-02 09:34:50|提交申请;
-钟洪伟|审批人|2025-07-02 13:15:40|同意;
-董磊|直接主管|2025-07-02 13:33:46|同意;
-曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-07-02 13:33:46|抄送</t>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>钟洪伟,董磊</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>50:38:48</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>段少波|提交申请|2025-08-02 08:41:29|提交申请;
+钟洪伟|审批人|2025-08-04 07:03:24|同意|;
+董磊|直接主管|2025-08-04 11:20:17|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-04 11:20:17|抄送</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>POafn6oZQ4yutkj4beOrFQ06491751333203</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>协助随州生产线运行工艺，保障7月份生产订单交付</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>汽车</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>qa07YJnjSRuYVZZZBSa6aA06491754046544</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>出差随州重卡桥线建设投产及共线EA3800N项目技改</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>火车</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>单程</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>随州市</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>随州市</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2025-07-01 上午</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2025-07-31 下午</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>协助随州生产线运行工艺，保障7月份生产订单交付</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>随州</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-08-01 上午</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-08-07 下午</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>杭州时代电动科技有限公司</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>宁德时代电动科技有限公司</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>202507010926000435698</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2025-07-01 09:26:43</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>祝叶康</t>
-        </is>
-      </c>
-      <c r="T5"/>
-      <c r="U5" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>202508011909000043699</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2025-08-01 19:09:04</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>胡俊杨</t>
+        </is>
+      </c>
+      <c r="T12"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>审批通过</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>已结束</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>2025-07-01 09:33:47</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>工艺技术部</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>祝叶康提交的出差</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2025-08-03 10:03:25</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>胡俊杨提交的出差</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>董磊</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>0:7:4</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>祝叶康|提交申请|2025-07-01 09:26:43|提交申请;
-董磊|审批人|2025-07-01 09:33:47|同意;
-董磊|直接主管|2025-07-01 09:33:47|同意;
-曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-07-01 09:33:47|抄送</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PclgkkmaSyGlZGuwTC_NOg06491751333097</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>出差随州重卡桥线建设投产及共线EA3800N项目技改</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>火车</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>单程</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>随州</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2025-07-01 上午</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2025-07-31 下午</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>杭州时代电动科技有限公司</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>宁德时代电动科技有限公司</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>202507010924000578122</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2025-07-01 09:24:57</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>胡俊杨</t>
-        </is>
-      </c>
-      <c r="T6"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>审批通过</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>已结束</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2025-07-01 09:33:50</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>工艺技术部</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>胡俊杨提交的出差</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>董磊</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>0:8:54</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>胡俊杨|提交申请|2025-07-01 09:24:57|提交申请;
-董磊|审批人|2025-07-01 09:33:50|同意;
-董磊|直接主管|2025-07-01 09:33:50|同意;
-曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-07-01 09:33:50|抄送</t>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>38:54:22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>胡俊杨(已离职)|提交申请|2025-08-01 19:09:04|提交申请;
+董磊|审批人|2025-08-03 10:03:26|同意;
+董磊|直接主管|2025-08-03 10:03:26|同意;
+曾婷婷,沈莉萍,李萍,周哲敏,尹娜,代远丽|抄送人|2025-08-03 10:03:26|抄送</t>
         </is>
       </c>
     </row>
